--- a/registro_gestion.xlsx
+++ b/registro_gestion.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -483,6 +483,34 @@
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>16/10/2026 17:45</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>38/15-0463-LPU26</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>EN SEGUIMIENTO</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Marcado desde dashboard</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
         <is>
           <t>No</t>
         </is>

--- a/registro_gestion.xlsx
+++ b/registro_gestion.xlsx
@@ -491,12 +491,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>16/10/2026 17:45</t>
+          <t>17/10/2026 08:46</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>38/15-0463-LPU26</t>
+          <t>38/12-0494-LPU26</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
